--- a/hira_material_automation/output/monthly/202601_202605__epidural_adhesion_barrier__900129__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202605__epidural_adhesion_barrier__900129__normalized.xlsx
@@ -431,7 +431,7 @@
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -486,7 +486,11 @@
           <t>900129</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>척추경막외 유착방지제</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>702</t>
@@ -519,7 +523,11 @@
           <t>900129</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>척추경막외 유착방지제</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>992</t>
@@ -552,7 +560,11 @@
           <t>900129</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>척추경막외 유착방지제</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>890</t>
@@ -625,7 +637,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-04T22:37:05</t>
+          <t>2026-05-14T22:45:19</t>
         </is>
       </c>
     </row>
@@ -637,7 +649,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>d10bc8682ee095f7496ff57061b8da016415e6d4264fb9f54292a4732c07e316</t>
+          <t>79228b5eb88d2e79cfa7b8713ad94cb2a3125f6ed75cb6e5c0bc563b095f82c3</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202605__epidural_adhesion_barrier__900129__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202605__epidural_adhesion_barrier__900129__normalized.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-14T22:45:19</t>
+          <t>2026-05-24T22:30:02</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>79228b5eb88d2e79cfa7b8713ad94cb2a3125f6ed75cb6e5c0bc563b095f82c3</t>
+          <t>d74eaeb45f742162847fb9164b77887470bdc964ea35c8cf1a3c2307969dd585</t>
         </is>
       </c>
     </row>
